--- a/erp-server/erp-server-file/src/main/resources/excel/tms/inventorySkuCostExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/inventorySkuCostExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>单据编号</t>
   </si>
@@ -43,13 +43,22 @@
     <t>成本组织</t>
   </si>
   <si>
+    <t>仓库</t>
+  </si>
+  <si>
     <t>SKU</t>
   </si>
   <si>
     <t>产品名称</t>
   </si>
   <si>
-    <t>单位成本</t>
+    <t>材料成本</t>
+  </si>
+  <si>
+    <t>头程运费</t>
+  </si>
+  <si>
+    <t>清关税费</t>
   </si>
   <si>
     <t>创建人</t>
@@ -70,6 +79,9 @@
     <t>{.companyName}</t>
   </si>
   <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
@@ -77,6 +89,12 @@
   </si>
   <si>
     <t>{.productCostStr}</t>
+  </si>
+  <si>
+    <t>{.firstMileShippingCostStr}</t>
+  </si>
+  <si>
+    <t>{.clearanceCustomsTaxStr}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1039,21 +1057,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="20.5" customWidth="1"/>
-    <col min="7" max="7" width="23.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" customWidth="1"/>
-    <col min="9" max="9" width="19.375" customWidth="1"/>
+    <col min="4" max="5" width="21.625" customWidth="1"/>
+    <col min="6" max="6" width="18.875" customWidth="1"/>
+    <col min="7" max="7" width="20.5" customWidth="1"/>
+    <col min="8" max="8" width="23.625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="21.625" customWidth="1"/>
+    <col min="11" max="11" width="20.375" customWidth="1"/>
+    <col min="12" max="12" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1066,49 +1085,67 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="6" t="s">
         <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/inventorySkuCostExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/inventorySkuCostExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>单据编号</t>
   </si>
@@ -40,6 +40,9 @@
     <t>分摊月份</t>
   </si>
   <si>
+    <t>核算月份</t>
+  </si>
+  <si>
     <t>成本组织</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
   </si>
   <si>
     <t>{.allocatedMonthStr}</t>
+  </si>
+  <si>
+    <t>{.accountingMonthStr}</t>
   </si>
   <si>
     <t>{.companyName}</t>
@@ -1057,22 +1063,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="21.625" customWidth="1"/>
-    <col min="6" max="6" width="18.875" customWidth="1"/>
-    <col min="7" max="7" width="20.5" customWidth="1"/>
-    <col min="8" max="8" width="23.625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.625" customWidth="1"/>
-    <col min="11" max="11" width="20.375" customWidth="1"/>
-    <col min="12" max="12" width="19.375" customWidth="1"/>
+    <col min="3" max="4" width="21" customWidth="1"/>
+    <col min="5" max="6" width="21.625" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="20.5" customWidth="1"/>
+    <col min="9" max="9" width="23.625" style="1" customWidth="1"/>
+    <col min="10" max="11" width="21.625" customWidth="1"/>
+    <col min="12" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="13" width="19.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1088,64 +1094,70 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
         <v>20</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
       <c r="L2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
